--- a/artfynd/A 9222-2025 artfynd.xlsx
+++ b/artfynd/A 9222-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123227786</v>
+        <v>123226811</v>
       </c>
       <c r="B2" t="n">
         <v>98365</v>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>542895</v>
+        <v>542904</v>
       </c>
       <c r="R2" t="n">
-        <v>6712254</v>
+        <v>6712270</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,12 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:12</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Cirka 1-1,5 m2.</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,12 +780,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn</t>
+          <t>Lisa Olson, Cecilia Rastad, Göran Ehn</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -914,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123226811</v>
+        <v>123226047</v>
       </c>
       <c r="B4" t="n">
-        <v>98365</v>
+        <v>5173</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,45 +921,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Björkberget, Björkberget, Dlr</t>
+          <t>Kroken, Vika, Kroken, Vika, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>542904</v>
+        <v>542891</v>
       </c>
       <c r="R4" t="n">
-        <v>6712270</v>
+        <v>6712281</v>
       </c>
       <c r="S4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -993,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,29 +1003,28 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lisa Olson, Cecilia Rastad, Göran Ehn</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123226047</v>
+        <v>123227786</v>
       </c>
       <c r="B5" t="n">
-        <v>5173</v>
+        <v>98365</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1043,38 +1033,42 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kroken, Vika, Kroken, Vika, Dlr</t>
+          <t>Björkberget, Björkberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>542891</v>
+        <v>542895</v>
       </c>
       <c r="R5" t="n">
-        <v>6712281</v>
+        <v>6712254</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1116,7 +1110,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Cirka 1-1,5 m2.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1125,6 +1124,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 9222-2025 artfynd.xlsx
+++ b/artfynd/A 9222-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123226811</v>
+        <v>123227786</v>
       </c>
       <c r="B2" t="n">
         <v>98365</v>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>542904</v>
+        <v>542895</v>
       </c>
       <c r="R2" t="n">
-        <v>6712270</v>
+        <v>6712254</v>
       </c>
       <c r="S2" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +764,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Cirka 1-1,5 m2.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,19 +785,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lisa Olson, Cecilia Rastad, Göran Ehn</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123226277</v>
+        <v>123226811</v>
       </c>
       <c r="B3" t="n">
         <v>98365</v>
@@ -836,13 +841,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>542911</v>
+        <v>542904</v>
       </c>
       <c r="R3" t="n">
-        <v>6712261</v>
+        <v>6712270</v>
       </c>
       <c r="S3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1021,7 +1026,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123227786</v>
+        <v>123226277</v>
       </c>
       <c r="B5" t="n">
         <v>98365</v>
@@ -1065,13 +1070,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>542895</v>
+        <v>542911</v>
       </c>
       <c r="R5" t="n">
-        <v>6712254</v>
+        <v>6712261</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1100,7 +1105,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,12 +1115,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:12</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Cirka 1-1,5 m2.</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,12 +1131,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn</t>
+          <t>Lisa Olson, Cecilia Rastad, Göran Ehn</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 9222-2025 artfynd.xlsx
+++ b/artfynd/A 9222-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123227786</v>
+        <v>123226277</v>
       </c>
       <c r="B2" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>542895</v>
+        <v>542911</v>
       </c>
       <c r="R2" t="n">
-        <v>6712254</v>
+        <v>6712261</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,12 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:12</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Cirka 1-1,5 m2.</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,22 +780,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn</t>
+          <t>Lisa Olson, Cecilia Rastad, Göran Ehn</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123226811</v>
+        <v>123227786</v>
       </c>
       <c r="B3" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -841,13 +836,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>542904</v>
+        <v>542895</v>
       </c>
       <c r="R3" t="n">
-        <v>6712270</v>
+        <v>6712254</v>
       </c>
       <c r="S3" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +881,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Cirka 1-1,5 m2.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,22 +902,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lisa Olson, Cecilia Rastad, Göran Ehn</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123226047</v>
+        <v>123226811</v>
       </c>
       <c r="B4" t="n">
-        <v>5173</v>
+        <v>98368</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,41 +926,45 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kroken, Vika, Kroken, Vika, Dlr</t>
+          <t>Björkberget, Björkberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>542891</v>
+        <v>542904</v>
       </c>
       <c r="R4" t="n">
-        <v>6712281</v>
+        <v>6712270</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -989,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +1003,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,28 +1012,29 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn</t>
+          <t>Lisa Olson, Cecilia Rastad, Göran Ehn</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123226277</v>
+        <v>123226047</v>
       </c>
       <c r="B5" t="n">
-        <v>98365</v>
+        <v>5173</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1038,45 +1043,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Björkberget, Björkberget, Dlr</t>
+          <t>Kroken, Vika, Kroken, Vika, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>542911</v>
+        <v>542891</v>
       </c>
       <c r="R5" t="n">
-        <v>6712261</v>
+        <v>6712281</v>
       </c>
       <c r="S5" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1124,19 +1125,18 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Lisa Olson, Cecilia Rastad, Göran Ehn</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 9222-2025 artfynd.xlsx
+++ b/artfynd/A 9222-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123226277</v>
       </c>
       <c r="B2" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123227786</v>
+        <v>123226811</v>
       </c>
       <c r="B3" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -836,13 +836,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>542895</v>
+        <v>542904</v>
       </c>
       <c r="R3" t="n">
-        <v>6712254</v>
+        <v>6712270</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,12 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:12</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Cirka 1-1,5 m2.</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,22 +897,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn</t>
+          <t>Lisa Olson, Cecilia Rastad, Göran Ehn</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123226811</v>
+        <v>123226047</v>
       </c>
       <c r="B4" t="n">
-        <v>98368</v>
+        <v>5173</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,45 +921,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Björkberget, Björkberget, Dlr</t>
+          <t>Kroken, Vika, Kroken, Vika, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>542904</v>
+        <v>542891</v>
       </c>
       <c r="R4" t="n">
-        <v>6712270</v>
+        <v>6712281</v>
       </c>
       <c r="S4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -993,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,29 +1003,28 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lisa Olson, Cecilia Rastad, Göran Ehn</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123226047</v>
+        <v>123227786</v>
       </c>
       <c r="B5" t="n">
-        <v>5173</v>
+        <v>98370</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1043,38 +1033,42 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kroken, Vika, Kroken, Vika, Dlr</t>
+          <t>Björkberget, Björkberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>542891</v>
+        <v>542895</v>
       </c>
       <c r="R5" t="n">
-        <v>6712281</v>
+        <v>6712254</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1116,7 +1110,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Cirka 1-1,5 m2.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1125,6 +1124,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 9222-2025 artfynd.xlsx
+++ b/artfynd/A 9222-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123226277</v>
+        <v>123227786</v>
       </c>
       <c r="B2" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>542911</v>
+        <v>542895</v>
       </c>
       <c r="R2" t="n">
-        <v>6712261</v>
+        <v>6712254</v>
       </c>
       <c r="S2" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +764,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Cirka 1-1,5 m2.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,12 +785,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lisa Olson, Cecilia Rastad, Göran Ehn</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -795,7 +800,7 @@
         <v>123226811</v>
       </c>
       <c r="B3" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -902,7 +907,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lisa Olson, Cecilia Rastad, Göran Ehn</t>
+          <t>Lisa Olson, Göran Ehn, Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1021,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123227786</v>
+        <v>123226277</v>
       </c>
       <c r="B5" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1065,13 +1070,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>542895</v>
+        <v>542911</v>
       </c>
       <c r="R5" t="n">
-        <v>6712254</v>
+        <v>6712261</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1100,7 +1105,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,12 +1115,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:12</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Cirka 1-1,5 m2.</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,12 +1131,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn</t>
+          <t>Lisa Olson, Cecilia Rastad, Göran Ehn</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 9222-2025 artfynd.xlsx
+++ b/artfynd/A 9222-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123227786</v>
+        <v>123226811</v>
       </c>
       <c r="B2" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>542895</v>
+        <v>542904</v>
       </c>
       <c r="R2" t="n">
-        <v>6712254</v>
+        <v>6712270</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,12 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:12</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Cirka 1-1,5 m2.</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,12 +780,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn</t>
+          <t>Lisa Olson, Cecilia Rastad, Göran Ehn</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -800,7 +795,7 @@
         <v>123226277</v>
       </c>
       <c r="B3" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -917,7 +912,7 @@
         <v>123226047</v>
       </c>
       <c r="B4" t="n">
-        <v>5173</v>
+        <v>5174</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1026,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123226811</v>
+        <v>123227786</v>
       </c>
       <c r="B5" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1070,13 +1065,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>542904</v>
+        <v>542895</v>
       </c>
       <c r="R5" t="n">
-        <v>6712270</v>
+        <v>6712254</v>
       </c>
       <c r="S5" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1105,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1115,7 +1110,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Cirka 1-1,5 m2.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,12 +1131,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Lisa Olson, Cecilia Rastad, Göran Ehn</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 9222-2025 artfynd.xlsx
+++ b/artfynd/A 9222-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123226811</v>
+        <v>123226277</v>
       </c>
       <c r="B2" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>542904</v>
+        <v>542911</v>
       </c>
       <c r="R2" t="n">
-        <v>6712270</v>
+        <v>6712261</v>
       </c>
       <c r="S2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123226277</v>
+        <v>123227786</v>
       </c>
       <c r="B3" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -836,13 +836,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>542911</v>
+        <v>542895</v>
       </c>
       <c r="R3" t="n">
-        <v>6712261</v>
+        <v>6712254</v>
       </c>
       <c r="S3" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +881,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Cirka 1-1,5 m2.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,22 +902,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lisa Olson, Cecilia Rastad, Göran Ehn</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123226047</v>
+        <v>123226811</v>
       </c>
       <c r="B4" t="n">
-        <v>5174</v>
+        <v>98502</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,41 +926,45 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kroken, Vika, Kroken, Vika, Dlr</t>
+          <t>Björkberget, Björkberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>542891</v>
+        <v>542904</v>
       </c>
       <c r="R4" t="n">
-        <v>6712281</v>
+        <v>6712270</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +1003,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,28 +1012,29 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn</t>
+          <t>Lisa Olson, Cecilia Rastad, Göran Ehn</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123227786</v>
+        <v>123226047</v>
       </c>
       <c r="B5" t="n">
-        <v>98396</v>
+        <v>5176</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,42 +1043,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Björkberget, Björkberget, Dlr</t>
+          <t>Kroken, Vika, Kroken, Vika, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>542895</v>
+        <v>542891</v>
       </c>
       <c r="R5" t="n">
-        <v>6712254</v>
+        <v>6712281</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,7 +1106,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,12 +1116,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:12</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Cirka 1-1,5 m2.</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1124,7 +1125,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 9222-2025 artfynd.xlsx
+++ b/artfynd/A 9222-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123226277</v>
       </c>
       <c r="B2" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123227786</v>
+        <v>123226811</v>
       </c>
       <c r="B3" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -836,13 +836,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>542895</v>
+        <v>542904</v>
       </c>
       <c r="R3" t="n">
-        <v>6712254</v>
+        <v>6712270</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,12 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:12</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Cirka 1-1,5 m2.</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,22 +897,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn</t>
+          <t>Lisa Olson, Cecilia Rastad, Göran Ehn</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123226811</v>
+        <v>123226047</v>
       </c>
       <c r="B4" t="n">
-        <v>98502</v>
+        <v>5176</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,45 +921,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Björkberget, Björkberget, Dlr</t>
+          <t>Kroken, Vika, Kroken, Vika, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>542904</v>
+        <v>542891</v>
       </c>
       <c r="R4" t="n">
-        <v>6712270</v>
+        <v>6712281</v>
       </c>
       <c r="S4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -993,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,29 +1003,28 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lisa Olson, Cecilia Rastad, Göran Ehn</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123226047</v>
+        <v>123227786</v>
       </c>
       <c r="B5" t="n">
-        <v>5176</v>
+        <v>98504</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1043,38 +1033,42 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kroken, Vika, Kroken, Vika, Dlr</t>
+          <t>Björkberget, Björkberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>542891</v>
+        <v>542895</v>
       </c>
       <c r="R5" t="n">
-        <v>6712281</v>
+        <v>6712254</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1116,7 +1110,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Cirka 1-1,5 m2.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1125,6 +1124,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 9222-2025 artfynd.xlsx
+++ b/artfynd/A 9222-2025 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123226811</v>
+        <v>123226047</v>
       </c>
       <c r="B3" t="n">
-        <v>98504</v>
+        <v>5176</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,45 +804,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Björkberget, Björkberget, Dlr</t>
+          <t>Kroken, Vika, Kroken, Vika, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>542904</v>
+        <v>542891</v>
       </c>
       <c r="R3" t="n">
-        <v>6712270</v>
+        <v>6712281</v>
       </c>
       <c r="S3" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,29 +886,28 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lisa Olson, Cecilia Rastad, Göran Ehn</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123226047</v>
+        <v>123226811</v>
       </c>
       <c r="B4" t="n">
-        <v>5176</v>
+        <v>98504</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,41 +916,45 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kroken, Vika, Kroken, Vika, Dlr</t>
+          <t>Björkberget, Björkberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>542891</v>
+        <v>542904</v>
       </c>
       <c r="R4" t="n">
-        <v>6712281</v>
+        <v>6712270</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,18 +1002,19 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn</t>
+          <t>Lisa Olson, Cecilia Rastad, Göran Ehn</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
